--- a/常見的AI應用/實戰範例/薪資計算表/素材_員工出勤與設定明細.xlsx
+++ b/常見的AI應用/實戰範例/薪資計算表/素材_員工出勤與設定明細.xlsx
@@ -77,7 +77,7 @@
       <name val="微軟正黑體"/>
       <b val="1"/>
       <color rgb="001F4E79"/>
-      <sz val="12"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="12">
@@ -276,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -340,8 +340,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -753,28 +755,28 @@
           <t>員工基本資料</t>
         </is>
       </c>
-      <c r="B4" s="31" t="n"/>
-      <c r="C4" s="32" t="n"/>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="34" t="n"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>一、應發薪資項目（A）</t>
         </is>
       </c>
-      <c r="E4" s="31" t="n"/>
-      <c r="F4" s="31" t="n"/>
-      <c r="G4" s="31" t="n"/>
-      <c r="H4" s="32" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="34" t="n"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
           <t>二、法定與出勤應扣項目（B）</t>
         </is>
       </c>
-      <c r="J4" s="31" t="n"/>
-      <c r="K4" s="31" t="n"/>
-      <c r="L4" s="31" t="n"/>
-      <c r="M4" s="31" t="n"/>
-      <c r="N4" s="31" t="n"/>
-      <c r="O4" s="32" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="34" t="n"/>
       <c r="P4" s="3" t="inlineStr">
         <is>
           <t>三、實領金額（A-B）</t>
@@ -1755,8 +1757,8 @@
           <t>合計 (12 位員工總額)</t>
         </is>
       </c>
-      <c r="B18" s="33" t="n"/>
-      <c r="C18" s="34" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="36" t="n"/>
       <c r="D18" s="15">
         <f>SUM(D6:D17)</f>
         <v/>
@@ -1908,7 +1910,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>會計作業指引：每日僅需填寫「正常工時」與「當日加班時數(F欄)」，G欄(前2H)與H欄(超2H)由公式自動拆解！月底總表自動加總</t>
+          <t>會計操作：不需照順序！只要填寫「正常工時」與「當日加班時數(F欄)」，G欄(前2H)與H欄(超2H)自動拆分！月底總表自動加總</t>
         </is>
       </c>
     </row>
@@ -19915,135 +19917,301 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="135" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>【12位員工日薪制出勤與薪資計算系統 使用說明書】</t>
+          <t>【12位員工日薪制出勤與薪資計算系統 —— 會計新手超詳細操作指南】</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="29" t="inlineStr">
         <is>
-          <t>一、系統架構與特色</t>
+          <t>一、給會計新手的 3 個核心觀念（放輕鬆，這張表很聰明！）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
         <is>
-          <t>本活頁簿專為中小企業、工廠、工程團隊之「日薪制」員工設計，包含 4 個相互勾稽的工作表：</t>
+          <t>1. 【您只要負責填基本數字】：例如今天上班幾小時、加班幾小時。其餘所有計算（算時薪、算加班倍率、扣勞健保、算實領）全部由電腦公式自動完成！</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="30" t="inlineStr">
         <is>
-          <t>1. 【月薪資總表】：每月發薪總表，全自動公式匯總應發、應扣、實領與雇主提撥，並具備 12 位員工合計與核決簽章欄。</t>
+          <t>2. 【千萬不要手動去改有公式的格子】：凡是有底色、或是您點進去看到上方編輯列有「=SUM(...)」或「=IF(...)」的格子，電腦會自己算，請不要手動打字覆蓋它！</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="30" t="inlineStr">
         <is>
-          <t>2. 【每日出勤】：1日～30/31日全月出勤日誌。會計每天只要輸入「當日加班總時數」，系統自動拆解「前2小時」與「超過2小時」，徹底解決加班費跨日分段加乘難題！</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="30" t="inlineStr">
-        <is>
-          <t>3. 【員工設定】：維護 12 位員工投保級距、自付額、雇主提撥額與自提率，避免每月重複手動設定。</t>
+          <t>3. 【月薪資總表會自動雷達偵測】：您在「每日出勤」隨便改一個數字，「月薪資總表」在一秒之內就會自動同步變更，完全不需要手動複製貼上！</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
-        <is>
-          <t>4. 【使用說明】：本系統所有計算公式、勞動法規標準與會計操作規範之指引。</t>
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>二、出納 / 會計日常操作 3 步驟（照著做絕不出錯）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>【步驟 1：月初或有人員變動時】➔ 檢查「員工設定」工作表</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>二、關鍵！每日加班拆解核心公式</t>
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 每年初或新員工入職時，進來設定一次：員工姓名、投保級距（勞保、健保、勞退提繳）。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="30" t="inlineStr">
         <is>
-          <t>勞動基準法第 24 條明定延長工作時間之加給係「按日」計算，不可將整月加班時數累加後才拆算：</t>
+          <t xml:space="preserve">   - ⚠️ 特別注意：『員工編號』（例如 EMP01, EMP02）是全系統的靈魂身分證字號，請確保各表一致，不要隨意打錯或加空格！</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>1. 當日前 2 小時加班公式：=IF(F5&gt;0, MIN(F5, 2), 0)</t>
-        </is>
-      </c>
+      <c r="A12" s="30" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 若當日加班 1 小時 ➔ 自動判定為前2小時 = 1H，超2小時 = 0H</t>
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>【步驟 2：每天最主要的登記工作】➔ 填寫「每日出勤」工作表</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 若當日加班 3.5 小時 ➔ 自動判定為前2小時 = 2H，超2小時 = 1.5H</t>
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - ❓ 重要問答：每天登記『一定要照日期或員工順序嗎？』</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>2. 當日超過 2 小時加班公式：=IF(F5&gt;2, F5-2, 0)</t>
+          <t xml:space="preserve">     👉 答案：【完全不需要照順序！】想怎麼記就怎麼記！</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>3. 月底加總：月薪資總表使用 SUMIF 分別加總整月份所有工作日之「前2小時累計」與「超2小時累計」，算式 100% 合規精準！</t>
+          <t xml:space="preserve">     👉 原因：後台月總表是用『SUMIF（條件搜尋加總）』，電腦只認『員工編號』，完全不在乎資料排在第幾行、也不在乎日期先後！</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     👉 操作方式 A（推薦流水帳）：今天誰有上班、誰有加班，直接在最下方空列填一行。今天漏記了前天補打也可以！</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>三、會計日常與月底作業 SOP</t>
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     👉 操作方式 B（預排表格）：直接滑鼠滾動到今天的日期，在對應員工那一行填入數字。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>步驟 1【月初/異動】：若有新進員工或勞健保投保級距調整，於「員工設定」表更新基本資料。</t>
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - ❓ 關鍵技巧：『加班時數怎麼填？需要自己心算拆 1.33 和 1.66 嗎？』</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t>步驟 2【每日登記】：出納/現場主管每日至「每日出勤」工作表，依員工編號填寫工時、加班（只需填一個總數）與請假/預支。</t>
+          <t xml:space="preserve">     👉 答案：【絕對不要自己心算！】您只要在『當日加班總時數 (F欄)』填入一個總數（例如加班 3 小時填 3，加班 3.5 小時填 3.5）。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="30" t="inlineStr">
         <is>
-          <t>步驟 3【月底結算】：進入「月薪資總表」，確認每位員工工時與金額已自動匯總平帳，核對總額與簽章送審。</t>
+          <t xml:space="preserve">     👉 電腦會自動在 G 欄幫您填入『前2小時 = 2』，在 H 欄幫您填入『超過2小時 = 1.5』！</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - ❓ 新手實用密技：『如果自己在最下面新加了一行，後面的自動拆分公式沒跑出來怎麼辦？』</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     👉 密技：滑鼠選取上一行的格子，按下鍵盤上的【Ctrl + D】（向下填滿），公式就瞬間自動複製下來了！</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - ❓ 預支或借支扣款：</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     👉 若員工在月中借支 1,000 元，直接在『預支/代扣款 (K欄)』輸入 1000，備註寫『月中預支』。月底總表會全自動從實領中扣除，保證不呆帳！</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>【步驟 3：月底結算與發薪】➔ 查看與列印「月薪資總表」</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 月底一到，點進「月薪資總表」，此時所有員工的出勤天數、餐費補助、加班費、請假扣薪、實領薪資已 100% 自動算好！</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 會計只要花 10 秒核對：最底部的『合計』實領薪資總額，是否與公司準備發放的現金或轉帳總額一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 直接按列印（Ctrl + P），交給主管簽章（核准、覆核、審核、製表），結算大功告成！</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>三、新手常見問題與避坑指南（救急 Q&amp;A）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>Q1：我不小心把某個格子的公式刪掉了，變成一片空白，怎麼辦？</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   👉 救命快捷鍵：立刻按下鍵盤上的【Ctrl + Z】（復原上一步），公式就會立刻變回來！</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   👉 備用救法：如果已經存檔關閉了，可以點選上一行正常的格子，按下鍵盤【Ctrl + D】，公式就會重新複製下來。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>Q2：為什麼加班費算出來會有小數點？</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   👉 說明：因為法定倍率是 1.3333... 與 1.6666...，公式內部已經幫您寫了【ROUND(..., 0)】（自動四捨五入到個位數），不用擔心小數點問題！</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="30" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>Q3：勞退雇主提撥 6% 為什麼寫在最右邊？會扣到員工的薪水嗎？</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   👉 說明：【絕對不會扣員工薪水！】勞退 6% 依照勞工退休金條例是『老闆要額外付的法定成本』，依法嚴禁從員工薪水扣！</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   👉 總表特別列出來，是為了讓老闆或財務主管每個月能一眼看出『公司這個月實際的人事總成本是多少』，避免少估成本。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>四、新手必備 4 個 Excel 鍵盤快捷鍵（記住這 4 個，操作快十倍！）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t>1. 【Ctrl + Z】：按錯了、不小心刪掉了？按它立刻『復原上一步』！</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>2. 【Ctrl + D】：選取上一格按它，立刻『把上一格的內容或公式直接複製下來』！</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="32" t="inlineStr">
+        <is>
+          <t>3. 【Ctrl + F】：資料好多找不到某個員工？按它輸入員工姓名或編號，立刻『快速搜尋跳過去』！</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t>4. 【Ctrl + S】：做完一部分就隨手按一下，立刻『存檔』，預防電腦當機資料遺失！</t>
         </is>
       </c>
     </row>
